--- a/profile.xlsx
+++ b/profile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e15030220\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E35B2EED-1B54-49B2-AB9F-D2659BCB3593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EBFB147-7197-45F1-AB9A-2318AF2045F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{0969AA7B-3DF2-4FE1-B394-AA9C10946B7C}"/>
+    <workbookView xWindow="-216" yWindow="924" windowWidth="13020" windowHeight="9420" xr2:uid="{0969AA7B-3DF2-4FE1-B394-AA9C10946B7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,18 +44,6 @@
     <t>Code</t>
   </si>
   <si>
-    <t xml:space="preserve">if ~isempty(idxSTP) </t>
-  </si>
-  <si>
-    <t>syn.x(idxSTP) = syn.x(idxSTP) + single(dt .* ((1 - double(syn.x(idxSTP))) ./ syn.tauX(idxSTP)));</t>
-  </si>
-  <si>
-    <t>syn.x(idxSTP) = min(max(syn.x(idxSTP), 0), 5);</t>
-  </si>
-  <si>
-    <t>idxSTP = find(isFiniteTau);</t>
-  </si>
-  <si>
     <t>Calls</t>
   </si>
   <si>
@@ -63,6 +51,18 @@
   </si>
   <si>
     <t>% Time</t>
+  </si>
+  <si>
+    <t>xstp = double(syn.x(idxSTP));</t>
+  </si>
+  <si>
+    <t>syn.x(idxSTP) = single(xstp);</t>
+  </si>
+  <si>
+    <t>xstp = xstp + ((1 - xstp) .* invTauDt);</t>
+  </si>
+  <si>
+    <t>Bnmda = 1 ./ (1 + exp(-0.062*v)/3.57);</t>
   </si>
 </sst>
 </file>
@@ -439,7 +439,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="73.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.33203125" customWidth="1"/>
     <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -451,84 +451,85 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>846</v>
+        <v>878</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>10001</v>
+        <v>20000</v>
       </c>
       <c r="D2">
-        <v>174.45</v>
+        <v>22.385999999999999</v>
       </c>
       <c r="E2" s="1">
-        <v>0.79200000000000004</v>
+        <v>0.32200000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>847</v>
+        <v>881</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="D3">
-        <v>15.36</v>
+        <v>20.39</v>
       </c>
       <c r="E3" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>0.29299999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>848</v>
+        <v>879</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="D4">
-        <v>7.27</v>
+        <v>8.5809999999999995</v>
       </c>
       <c r="E4" s="1">
-        <v>3.3000000000000002E-2</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>845</v>
+        <v>973</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>10001</v>
+        <v>20000</v>
       </c>
       <c r="D5">
-        <v>3.68</v>
+        <v>1.9790000000000001</v>
       </c>
       <c r="E5" s="1">
-        <v>1.7000000000000001E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>